--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="98">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -239,10 +239,79 @@
     <t>07.05.2026, 5, 11:25-12:10, sala: 44</t>
   </si>
   <si>
-    <t>07.05.2026, 5, 11:25-12:10, sala: kin</t>
+    <t>07.05.2026, 5, 11:25-12:10, sala: 2</t>
   </si>
   <si>
     <t>1TFA|JA1</t>
+  </si>
+  <si>
+    <t>08.05.2026, 1, 08:00-08:45, sala: 43</t>
+  </si>
+  <si>
+    <t>08.05.2026, 3, 09:40-10:25, sala: 43</t>
+  </si>
+  <si>
+    <t>Danielewski Paweł</t>
+  </si>
+  <si>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>08.05.2026, 8, 14:05-14:50, sala: 27</t>
+  </si>
+  <si>
+    <t>08.05.2026, 3, 09:40-10:25, sala: 27</t>
+  </si>
+  <si>
+    <t>Nowak Damiana</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>08.05.2026, 6, 12:25-13:10, sala: prF3</t>
+  </si>
+  <si>
+    <t>08.05.2026, 6, 12:25-13:10, sala: 3</t>
+  </si>
+  <si>
+    <t>2TFB</t>
+  </si>
+  <si>
+    <t>08.05.2026, 6, 12:25-13:10, sala: 40</t>
+  </si>
+  <si>
+    <t>08.05.2026, 6, 12:25-13:10, sala: 32</t>
+  </si>
+  <si>
+    <t>Jarek Zbigniew</t>
+  </si>
+  <si>
+    <t>1WA|JN1</t>
+  </si>
+  <si>
+    <t>Edukacja dla bezpieczeństwa</t>
+  </si>
+  <si>
+    <t>08.05.2026, 7, 13:15-14:00, sala: prF3</t>
+  </si>
+  <si>
+    <t>08.05.2026, 7, 13:15-14:00, sala: 3</t>
+  </si>
+  <si>
+    <t>08.05.2026, 8, 14:05-14:50, sala: 42</t>
+  </si>
+  <si>
+    <t>08.05.2026, 8, 14:05-14:50, sala: 5</t>
+  </si>
+  <si>
+    <t>Dalach Krystyna</t>
+  </si>
+  <si>
+    <t>1FA</t>
   </si>
 </sst>
 </file>
@@ -692,7 +761,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{028b4249-1ceb-4a84-85a8-770a65a39b86}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{7f943cc0-9b70-4a33-b80e-c56e09889c83}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -713,12 +782,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1ac437d3-d5b5-46ca-84b4-f8d6d90b0c0b}">
-  <dimension ref="A1:G20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{82f927a2-99a2-47d2-b02a-c948b480869f}">
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="31.4285714285714" customWidth="1"/>
+    <col min="1" max="1" width="32.5714285714286" customWidth="1"/>
+    <col min="2" max="2" width="30.7142857142857" customWidth="1"/>
     <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
@@ -1186,6 +1255,144 @@
         <v>15</v>
       </c>
     </row>
+    <row r="21" spans="1:7" ht="15">
+      <c r="A21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15">
+      <c r="A22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" t="s">
+        <v>83</v>
+      </c>
+      <c r="G22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15">
+      <c r="A23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" t="s">
+        <v>30</v>
+      </c>
+      <c r="G23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15">
+      <c r="A24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" t="s">
+        <v>91</v>
+      </c>
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15">
+      <c r="A25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15">
+      <c r="A26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -47,6 +47,42 @@
     <t>Uwagi</t>
   </si>
   <si>
+    <t>11.05.2026, 2, 08:50-09:35, sala: 27</t>
+  </si>
+  <si>
+    <t>11.05.2026, 6, 12:25-13:10, sala: 27</t>
+  </si>
+  <si>
+    <t>Karczmarz Aleksandra</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>1TH|JA2</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>p. Karczmarz, j. angielski za lekcję 2, sala 27</t>
+  </si>
+  <si>
+    <t>11.05.2026, 1, 08:00-08:45, sala: 18</t>
+  </si>
+  <si>
+    <t>11.05.2026, 7, 13:15-14:00, sala: 40</t>
+  </si>
+  <si>
+    <t>Jarek Zbigniew</t>
+  </si>
+  <si>
+    <t>Edukacja dla bezpieczeństwa</t>
+  </si>
+  <si>
+    <t>p. Jarek, EDB za lekcję 1, sala 40</t>
+  </si>
+  <si>
     <t>30.04.2026, 3, 09:40-10:25, sala: 43</t>
   </si>
   <si>
@@ -56,13 +92,7 @@
     <t>Staliś Donata</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>3TH|JA2</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
   </si>
   <si>
     <t>lekcja przeniesiona z czwartku 30 kwietnia na wtorek, 12 maja, lekcja 10</t>
@@ -515,7 +545,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{cdb3fbf6-ae0f-4135-8289-f57caa8f5f71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4355636a-bd72-4af7-871f-a7e797e00cbb}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -536,16 +566,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{327c0bbc-3bb8-4bbd-82d5-24b604e093d8}">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2cff0d9a-f5af-490a-8a4b-1b49026995ef}">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7142857142857" customWidth="1"/>
     <col min="2" max="2" width="31.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="20.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="14.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="26.7142857142857" customWidth="1"/>
     <col min="7" max="7" width="64" customWidth="1"/>
   </cols>
   <sheetData>
@@ -593,6 +623,52 @@
       </c>
       <c r="G2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -545,7 +545,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4355636a-bd72-4af7-871f-a7e797e00cbb}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1b03c61c-cf2e-437f-9568-beed252bcde9}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -566,7 +566,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2cff0d9a-f5af-490a-8a4b-1b49026995ef}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{3747d8ad-3e04-4125-8780-dd5b3b46b79b}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="74">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -96,6 +96,150 @@
   </si>
   <si>
     <t>lekcja przeniesiona z czwartku 30 kwietnia na wtorek, 12 maja, lekcja 10</t>
+  </si>
+  <si>
+    <t>13.05.2026, 1, 08:00-08:45, sala: 17</t>
+  </si>
+  <si>
+    <t>13.05.2026, 1, 08:00-08:45, sala: 32</t>
+  </si>
+  <si>
+    <t>Nowaczyk Agnieszka</t>
+  </si>
+  <si>
+    <t>4TFB</t>
+  </si>
+  <si>
+    <t>Język angielski zawodowy</t>
+  </si>
+  <si>
+    <t>przeniesienie do sali 32</t>
+  </si>
+  <si>
+    <t>13.05.2026, 2, 08:50-09:35, sala: 17</t>
+  </si>
+  <si>
+    <t>13.05.2026, 2, 08:50-09:35, sala: 32</t>
+  </si>
+  <si>
+    <t>13.05.2026, 4, 10:35-11:20, sala: 32</t>
+  </si>
+  <si>
+    <t>13.05.2026, 4, 10:35-11:20, sala: 27</t>
+  </si>
+  <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
+    <t>1S|JA2</t>
+  </si>
+  <si>
+    <t>lekcja przeniesiona do sali 27</t>
+  </si>
+  <si>
+    <t>13.05.2026, 5, 11:25-12:10, sala: 17</t>
+  </si>
+  <si>
+    <t>13.05.2026, 5, 11:25-12:10, sala: 34</t>
+  </si>
+  <si>
+    <t>Fiodorów Małgorzata</t>
+  </si>
+  <si>
+    <t>Język niemiecki</t>
+  </si>
+  <si>
+    <t>przeniesienie do sali 34</t>
+  </si>
+  <si>
+    <t>13.05.2026, 5, 11:25-12:10, sala: 43</t>
+  </si>
+  <si>
+    <t>13.05.2026, 5, 11:25-12:10, sala: 32</t>
+  </si>
+  <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>1TFA|JA2</t>
+  </si>
+  <si>
+    <t>lekcja przeniesiona do sali 32</t>
+  </si>
+  <si>
+    <t>13.05.2026, 5, 11:25-12:10, sala: 27</t>
+  </si>
+  <si>
+    <t>13.05.2026, 6, 12:25-13:10, sala: 17</t>
+  </si>
+  <si>
+    <t>13.05.2026, 6, 12:25-13:10, sala: 34</t>
+  </si>
+  <si>
+    <t>3TFA|JA1</t>
+  </si>
+  <si>
+    <t>13.05.2026, 6, 12:25-13:10, sala: 43</t>
+  </si>
+  <si>
+    <t>13.05.2026, 6, 12:25-13:10, sala: 30</t>
+  </si>
+  <si>
+    <t>1TH|JA1</t>
+  </si>
+  <si>
+    <t>lekcja przeniesiona do sali 30</t>
+  </si>
+  <si>
+    <t>14.05.2026, 2, 08:50-09:35, sala: 43</t>
+  </si>
+  <si>
+    <t>14.05.2026, 0, 07:10-07:55, sala: 27</t>
+  </si>
+  <si>
+    <t>1CB|JA1</t>
+  </si>
+  <si>
+    <t>14.05.2026, 3, 09:40-10:25, sala: 43</t>
+  </si>
+  <si>
+    <t>14.05.2026, 3, 09:40-10:25, sala: 27</t>
+  </si>
+  <si>
+    <t>1K|JA2</t>
+  </si>
+  <si>
+    <t>14.05.2026, 9, 14:55-15:40, sala: 38</t>
+  </si>
+  <si>
+    <t>14.05.2026, 4, 10:35-11:20, sala: 38</t>
+  </si>
+  <si>
+    <t>Taszycka Magdalena</t>
+  </si>
+  <si>
+    <t>1K|JA1</t>
+  </si>
+  <si>
+    <t>Informatyka</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>14.05.2026, 1, 08:00-08:45, sala: prs</t>
+  </si>
+  <si>
+    <t>14.05.2026, 7, 13:15-14:00, sala: prs</t>
+  </si>
+  <si>
+    <t>Filiczak Agnieszka</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>Technika w produkcji cukierniczej</t>
   </si>
 </sst>
 </file>
@@ -545,7 +689,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1b03c61c-cf2e-437f-9568-beed252bcde9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4e812725-b823-41e0-828a-c7758192d8b2}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -566,16 +710,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{3747d8ad-3e04-4125-8780-dd5b3b46b79b}">
-  <dimension ref="A1:G4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1ab0c26c-84a3-48fa-8be1-adb9b297fc9f}">
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="31.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="31.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="20.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="20.7142857142857" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="26.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="30.8571428571429" customWidth="1"/>
     <col min="7" max="7" width="64" customWidth="1"/>
   </cols>
   <sheetData>
@@ -671,6 +815,282 @@
         <v>25</v>
       </c>
     </row>
+    <row r="5" spans="1:7" ht="15">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15">
+      <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15">
+      <c r="A15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" t="s">
+        <v>73</v>
+      </c>
+      <c r="G16" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="69">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -122,82 +122,67 @@
     <t>13.05.2026, 2, 08:50-09:35, sala: 32</t>
   </si>
   <si>
-    <t>13.05.2026, 4, 10:35-11:20, sala: 32</t>
-  </si>
-  <si>
-    <t>13.05.2026, 4, 10:35-11:20, sala: 27</t>
-  </si>
-  <si>
-    <t>Wojciechowski Łukasz</t>
-  </si>
-  <si>
-    <t>1S|JA2</t>
+    <t>13.05.2026, 5, 11:25-12:10, sala: 17</t>
+  </si>
+  <si>
+    <t>13.05.2026, 5, 11:25-12:10, sala: 34</t>
+  </si>
+  <si>
+    <t>Fiodorów Małgorzata</t>
+  </si>
+  <si>
+    <t>Język niemiecki</t>
+  </si>
+  <si>
+    <t>przeniesienie do sali 34</t>
+  </si>
+  <si>
+    <t>13.05.2026, 5, 11:25-12:10, sala: 43</t>
+  </si>
+  <si>
+    <t>13.05.2026, 5, 11:25-12:10, sala: 32</t>
+  </si>
+  <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>1TFA|JA2</t>
+  </si>
+  <si>
+    <t>lekcja przeniesiona do sali 32</t>
+  </si>
+  <si>
+    <t>13.05.2026, 6, 12:25-13:10, sala: 17</t>
+  </si>
+  <si>
+    <t>13.05.2026, 6, 12:25-13:10, sala: 34</t>
+  </si>
+  <si>
+    <t>3TFA|JA1</t>
+  </si>
+  <si>
+    <t>13.05.2026, 6, 12:25-13:10, sala: 43</t>
+  </si>
+  <si>
+    <t>13.05.2026, 6, 12:25-13:10, sala: 30</t>
+  </si>
+  <si>
+    <t>1TH|JA1</t>
+  </si>
+  <si>
+    <t>lekcja przeniesiona do sali 30</t>
+  </si>
+  <si>
+    <t>14.05.2026, 2, 08:50-09:35, sala: 43</t>
+  </si>
+  <si>
+    <t>14.05.2026, 2, 08:50-09:35, sala: 27</t>
+  </si>
+  <si>
+    <t>1CB|JA1</t>
   </si>
   <si>
     <t>lekcja przeniesiona do sali 27</t>
-  </si>
-  <si>
-    <t>13.05.2026, 5, 11:25-12:10, sala: 17</t>
-  </si>
-  <si>
-    <t>13.05.2026, 5, 11:25-12:10, sala: 34</t>
-  </si>
-  <si>
-    <t>Fiodorów Małgorzata</t>
-  </si>
-  <si>
-    <t>Język niemiecki</t>
-  </si>
-  <si>
-    <t>przeniesienie do sali 34</t>
-  </si>
-  <si>
-    <t>13.05.2026, 5, 11:25-12:10, sala: 43</t>
-  </si>
-  <si>
-    <t>13.05.2026, 5, 11:25-12:10, sala: 32</t>
-  </si>
-  <si>
-    <t>Granatowska Mariola</t>
-  </si>
-  <si>
-    <t>1TFA|JA2</t>
-  </si>
-  <si>
-    <t>lekcja przeniesiona do sali 32</t>
-  </si>
-  <si>
-    <t>13.05.2026, 5, 11:25-12:10, sala: 27</t>
-  </si>
-  <si>
-    <t>13.05.2026, 6, 12:25-13:10, sala: 17</t>
-  </si>
-  <si>
-    <t>13.05.2026, 6, 12:25-13:10, sala: 34</t>
-  </si>
-  <si>
-    <t>3TFA|JA1</t>
-  </si>
-  <si>
-    <t>13.05.2026, 6, 12:25-13:10, sala: 43</t>
-  </si>
-  <si>
-    <t>13.05.2026, 6, 12:25-13:10, sala: 30</t>
-  </si>
-  <si>
-    <t>1TH|JA1</t>
-  </si>
-  <si>
-    <t>lekcja przeniesiona do sali 30</t>
-  </si>
-  <si>
-    <t>14.05.2026, 2, 08:50-09:35, sala: 43</t>
-  </si>
-  <si>
-    <t>14.05.2026, 0, 07:10-07:55, sala: 27</t>
-  </si>
-  <si>
-    <t>1CB|JA1</t>
   </si>
   <si>
     <t>14.05.2026, 3, 09:40-10:25, sala: 43</t>
@@ -689,7 +674,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4e812725-b823-41e0-828a-c7758192d8b2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{649e7da9-18fd-4676-9889-a21f621cf2f8}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -710,13 +695,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1ab0c26c-84a3-48fa-8be1-adb9b297fc9f}">
-  <dimension ref="A1:G16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ec087a14-72e9-4eba-93e7-2bab8fe2e176}">
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="31.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="20.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="20.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="30.8571428571429" customWidth="1"/>
@@ -875,10 +860,10 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
         <v>37</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
       </c>
       <c r="G7" t="s">
         <v>38</v>
@@ -898,10 +883,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
         <v>43</v>
@@ -915,50 +900,50 @@
         <v>45</v>
       </c>
       <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
         <v>46</v>
       </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>47</v>
-      </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G9" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
         <v>49</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>37</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
         <v>41</v>
@@ -967,128 +952,82 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15">
-      <c r="A15" t="s">
         <v>63</v>
-      </c>
-      <c r="B15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15">
-      <c r="A16" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -171,27 +171,6 @@
   </si>
   <si>
     <t>lekcja przeniesiona do sali 30</t>
-  </si>
-  <si>
-    <t>14.05.2026, 2, 08:50-09:35, sala: 43</t>
-  </si>
-  <si>
-    <t>14.05.2026, 2, 08:50-09:35, sala: 27</t>
-  </si>
-  <si>
-    <t>1CB|JA1</t>
-  </si>
-  <si>
-    <t>lekcja przeniesiona do sali 27</t>
-  </si>
-  <si>
-    <t>14.05.2026, 3, 09:40-10:25, sala: 43</t>
-  </si>
-  <si>
-    <t>14.05.2026, 3, 09:40-10:25, sala: 27</t>
-  </si>
-  <si>
-    <t>1K|JA2</t>
   </si>
   <si>
     <t>14.05.2026, 9, 14:55-15:40, sala: 38</t>
@@ -674,7 +653,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{649e7da9-18fd-4676-9889-a21f621cf2f8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c8b8a8b6-9c7a-432b-bf5f-4bab4582d3e4}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -695,8 +674,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ec087a14-72e9-4eba-93e7-2bab8fe2e176}">
-  <dimension ref="A1:G14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ad8e6621-d9ed-4193-88c0-e547c840e613}">
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.4285714285714" customWidth="1"/>
@@ -946,88 +925,42 @@
         <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" t="s">
         <v>56</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15">
-      <c r="A13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15">
-      <c r="A14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
   <si>
-    <t>Okres: 11.05.2026 (pon.) - 17.05.2026 (niedz.)</t>
+    <t>Okres: 18.05.2026 (pon.) - 24.05.2026 (niedz.)</t>
   </si>
   <si>
     <t>Przeniesiono z</t>
@@ -47,163 +47,103 @@
     <t>Uwagi</t>
   </si>
   <si>
-    <t>11.05.2026, 2, 08:50-09:35, sala: 27</t>
-  </si>
-  <si>
-    <t>11.05.2026, 6, 12:25-13:10, sala: 27</t>
-  </si>
-  <si>
-    <t>Karczmarz Aleksandra</t>
+    <t>18.05.2026, 8, 14:05-14:50, sala: prF3</t>
+  </si>
+  <si>
+    <t>18.05.2026, 7, 13:15-14:00, sala: prF3</t>
+  </si>
+  <si>
+    <t>Sobczak Anna</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>3FA</t>
+  </si>
+  <si>
+    <t>Techniki fryzjerskie</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>18.05.2026, 1, 08:00-08:45, sala: 18</t>
+  </si>
+  <si>
+    <t>18.05.2026, 10, 15:45-16:30, sala: 40</t>
+  </si>
+  <si>
+    <t>Jarek Zbigniew</t>
+  </si>
+  <si>
     <t>1TH|JA2</t>
   </si>
   <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>p. Karczmarz, j. angielski za lekcję 2, sala 27</t>
-  </si>
-  <si>
-    <t>11.05.2026, 1, 08:00-08:45, sala: 18</t>
-  </si>
-  <si>
-    <t>11.05.2026, 7, 13:15-14:00, sala: 40</t>
-  </si>
-  <si>
-    <t>Jarek Zbigniew</t>
-  </si>
-  <si>
     <t>Edukacja dla bezpieczeństwa</t>
   </si>
   <si>
-    <t>p. Jarek, EDB za lekcję 1, sala 40</t>
-  </si>
-  <si>
-    <t>30.04.2026, 3, 09:40-10:25, sala: 43</t>
-  </si>
-  <si>
-    <t>12.05.2026, 10, 15:45-16:30, sala: 43</t>
-  </si>
-  <si>
-    <t>Staliś Donata</t>
-  </si>
-  <si>
-    <t>3TH|JA2</t>
-  </si>
-  <si>
-    <t>lekcja przeniesiona z czwartku 30 kwietnia na wtorek, 12 maja, lekcja 10</t>
-  </si>
-  <si>
-    <t>13.05.2026, 1, 08:00-08:45, sala: 17</t>
-  </si>
-  <si>
-    <t>13.05.2026, 1, 08:00-08:45, sala: 32</t>
-  </si>
-  <si>
-    <t>Nowaczyk Agnieszka</t>
-  </si>
-  <si>
-    <t>4TFB</t>
-  </si>
-  <si>
-    <t>Język angielski zawodowy</t>
-  </si>
-  <si>
-    <t>przeniesienie do sali 32</t>
-  </si>
-  <si>
-    <t>13.05.2026, 2, 08:50-09:35, sala: 17</t>
-  </si>
-  <si>
-    <t>13.05.2026, 2, 08:50-09:35, sala: 32</t>
-  </si>
-  <si>
-    <t>13.05.2026, 5, 11:25-12:10, sala: 17</t>
-  </si>
-  <si>
-    <t>13.05.2026, 5, 11:25-12:10, sala: 34</t>
+    <t>lekcja przeniesiona na lekcję 10, sala 40</t>
+  </si>
+  <si>
+    <t>19.05.2026, 7, 13:15-14:00, sala: 17</t>
+  </si>
+  <si>
+    <t>19.05.2026, 2, 08:50-09:35, sala: 17</t>
   </si>
   <si>
     <t>Fiodorów Małgorzata</t>
   </si>
   <si>
+    <t>1TFB|JA1</t>
+  </si>
+  <si>
     <t>Język niemiecki</t>
   </si>
   <si>
-    <t>przeniesienie do sali 34</t>
-  </si>
-  <si>
-    <t>13.05.2026, 5, 11:25-12:10, sala: 43</t>
-  </si>
-  <si>
-    <t>13.05.2026, 5, 11:25-12:10, sala: 32</t>
-  </si>
-  <si>
-    <t>Granatowska Mariola</t>
-  </si>
-  <si>
-    <t>1TFA|JA2</t>
-  </si>
-  <si>
-    <t>lekcja przeniesiona do sali 32</t>
-  </si>
-  <si>
-    <t>13.05.2026, 6, 12:25-13:10, sala: 17</t>
-  </si>
-  <si>
-    <t>13.05.2026, 6, 12:25-13:10, sala: 34</t>
-  </si>
-  <si>
-    <t>3TFA|JA1</t>
-  </si>
-  <si>
-    <t>13.05.2026, 6, 12:25-13:10, sala: 43</t>
-  </si>
-  <si>
-    <t>13.05.2026, 6, 12:25-13:10, sala: 30</t>
-  </si>
-  <si>
-    <t>1TH|JA1</t>
-  </si>
-  <si>
-    <t>lekcja przeniesiona do sali 30</t>
-  </si>
-  <si>
-    <t>14.05.2026, 9, 14:55-15:40, sala: 38</t>
-  </si>
-  <si>
-    <t>14.05.2026, 4, 10:35-11:20, sala: 38</t>
-  </si>
-  <si>
-    <t>Taszycka Magdalena</t>
-  </si>
-  <si>
-    <t>1K|JA1</t>
-  </si>
-  <si>
-    <t>Informatyka</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>14.05.2026, 1, 08:00-08:45, sala: prs</t>
-  </si>
-  <si>
-    <t>14.05.2026, 7, 13:15-14:00, sala: prs</t>
-  </si>
-  <si>
-    <t>Filiczak Agnieszka</t>
-  </si>
-  <si>
-    <t>2CA</t>
-  </si>
-  <si>
-    <t>Technika w produkcji cukierniczej</t>
+    <t>lekcja przeniesiona na lekcję 2, sala 17</t>
+  </si>
+  <si>
+    <t>19.05.2026, 2, 08:50-09:35, sala: sg6</t>
+  </si>
+  <si>
+    <t>19.05.2026, 5, 11:25-12:10, sala: sg6</t>
+  </si>
+  <si>
+    <t>Pietrycha Małgorzata</t>
+  </si>
+  <si>
+    <t>2FB|DZ</t>
+  </si>
+  <si>
+    <t>Wychowanie fizyczne</t>
+  </si>
+  <si>
+    <t>20.05.2026, 2, 08:50-09:35, sala: 18</t>
+  </si>
+  <si>
+    <t>4TH</t>
+  </si>
+  <si>
+    <t>lekcja przeniesiona na środę 20 maja, lekcja 2, sala 18</t>
+  </si>
+  <si>
+    <t>18.05.2026, 3, 09:40-10:25, sala: 5</t>
+  </si>
+  <si>
+    <t>20.05.2026, 6, 12:25-13:10, sala: 3</t>
+  </si>
+  <si>
+    <t>Krzemińska Beata</t>
+  </si>
+  <si>
+    <t>3TFB</t>
+  </si>
+  <si>
+    <t>Projektowanie fryzur</t>
+  </si>
+  <si>
+    <t>lekcja przeniesiona na środę, 20 maja, lekcja 6, sala 3</t>
   </si>
 </sst>
 </file>
@@ -653,7 +593,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c8b8a8b6-9c7a-432b-bf5f-4bab4582d3e4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{11065fc1-0f4f-46ac-baea-15353b6561c3}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -674,17 +614,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ad8e6621-d9ed-4193-88c0-e547c840e613}">
-  <dimension ref="A1:G12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{614e898c-d97b-4bd5-98e7-5202230f3e32}">
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.4285714285714" customWidth="1"/>
-    <col min="2" max="2" width="31.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="20.4285714285714" customWidth="1"/>
+    <col min="1" max="2" width="32.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="19.8571428571429" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="30.8571428571429" customWidth="1"/>
-    <col min="7" max="7" width="64" customWidth="1"/>
+    <col min="6" max="6" width="26.7142857142857" customWidth="1"/>
+    <col min="7" max="7" width="47.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
@@ -747,220 +686,105 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15">
-      <c r="A8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" t="s">
         <v>41</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15">
-      <c r="A9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15">
-      <c r="A10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15">
-      <c r="A11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15">
-      <c r="A12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -119,13 +119,40 @@
     <t>Wychowanie fizyczne</t>
   </si>
   <si>
-    <t>20.05.2026, 2, 08:50-09:35, sala: 18</t>
+    <t>20.05.2026, 2, 08:50-09:35, sala: 17</t>
   </si>
   <si>
     <t>4TH</t>
   </si>
   <si>
-    <t>lekcja przeniesiona na środę 20 maja, lekcja 2, sala 18</t>
+    <t>20.05.2026, 1, 08:00-08:45, sala: 22</t>
+  </si>
+  <si>
+    <t>20.05.2026, 2, 08:50-09:35, sala: 22</t>
+  </si>
+  <si>
+    <t>Ulanowska Magdalena</t>
+  </si>
+  <si>
+    <t>2TH</t>
+  </si>
+  <si>
+    <t>Język polski</t>
+  </si>
+  <si>
+    <t>20.05.2026, 5, 11:25-12:10, sala: 17</t>
+  </si>
+  <si>
+    <t>20.05.2026, 5, 11:25-12:10, sala: 34</t>
+  </si>
+  <si>
+    <t>20.05.2026, 6, 12:25-13:10, sala: 17</t>
+  </si>
+  <si>
+    <t>20.05.2026, 6, 12:25-13:10, sala: 34</t>
+  </si>
+  <si>
+    <t>3TFA|JA1</t>
   </si>
   <si>
     <t>18.05.2026, 3, 09:40-10:25, sala: 5</t>
@@ -593,7 +620,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{11065fc1-0f4f-46ac-baea-15353b6561c3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0f3b7966-ada0-4af5-bfc0-0c531b540c72}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -614,16 +641,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{614e898c-d97b-4bd5-98e7-5202230f3e32}">
-  <dimension ref="A1:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b6f80500-2ac0-4267-972c-6c606f8faaca}">
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="32.5714285714286" customWidth="1"/>
-    <col min="3" max="3" width="19.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="26.7142857142857" customWidth="1"/>
-    <col min="7" max="7" width="47.7142857142857" customWidth="1"/>
+    <col min="7" max="7" width="47.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
@@ -761,30 +788,99 @@
         <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15">
       <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
         <v>39</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15">
+      <c r="A8" t="s">
         <v>40</v>
       </c>
-      <c r="G7" t="s">
+      <c r="B8" t="s">
         <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -138,6 +138,21 @@
   </si>
   <si>
     <t>Język polski</t>
+  </si>
+  <si>
+    <t>20.05.2026, 3, 09:40-10:25, sala: 40</t>
+  </si>
+  <si>
+    <t>20.05.2026, 3, 09:40-10:25, sala: bib</t>
+  </si>
+  <si>
+    <t>Socha Dariusz</t>
+  </si>
+  <si>
+    <t>Zajęcia biblioteczne</t>
+  </si>
+  <si>
+    <t>zaplanowano zastępstwo z nauczycielem Nowak Damiana [DW]</t>
   </si>
   <si>
     <t>20.05.2026, 5, 11:25-12:10, sala: 17</t>
@@ -620,7 +635,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0f3b7966-ada0-4af5-bfc0-0c531b540c72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a62f2def-e176-4d7f-b2ca-56070c05a219}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -641,8 +656,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b6f80500-2ac0-4267-972c-6c606f8faaca}">
-  <dimension ref="A1:G10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d5228173-3d02-41aa-a110-b2a22095be96}">
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="32.5714285714286" customWidth="1"/>
@@ -650,7 +665,7 @@
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="26.7142857142857" customWidth="1"/>
-    <col min="7" max="7" width="47.2857142857143" customWidth="1"/>
+    <col min="7" max="7" width="56.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
@@ -822,27 +837,27 @@
         <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
         <v>24</v>
@@ -851,7 +866,7 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
@@ -862,25 +877,48 @@
     </row>
     <row r="10" spans="1:7" ht="15">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="G10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15">
+      <c r="A11" t="s">
         <v>50</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -186,6 +186,24 @@
   </si>
   <si>
     <t>lekcja przeniesiona na środę, 20 maja, lekcja 6, sala 3</t>
+  </si>
+  <si>
+    <t>22.05.2026, 10, 15:45-16:30, sala: 19</t>
+  </si>
+  <si>
+    <t>22.05.2026, 5, 11:25-12:10, sala: 17</t>
+  </si>
+  <si>
+    <t>Biczysko Wojciech</t>
+  </si>
+  <si>
+    <t>1TH</t>
+  </si>
+  <si>
+    <t>Fizyka</t>
+  </si>
+  <si>
+    <t>p. Biczysko, za lekcję 10, sala 17</t>
   </si>
 </sst>
 </file>
@@ -635,7 +653,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a62f2def-e176-4d7f-b2ca-56070c05a219}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{89a34cc4-1fb2-4fa0-924e-7163f93c005b}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -656,8 +674,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d5228173-3d02-41aa-a110-b2a22095be96}">
-  <dimension ref="A1:G11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0adfa307-4275-44af-ae00-344989bf5983}">
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="32.5714285714286" customWidth="1"/>
@@ -921,6 +939,29 @@
         <v>55</v>
       </c>
     </row>
+    <row r="12" spans="1:7" ht="15">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="68">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -153,6 +153,24 @@
   </si>
   <si>
     <t>zaplanowano zastępstwo z nauczycielem Nowak Damiana [DW]</t>
+  </si>
+  <si>
+    <t>22.05.2026, 8, 14:05-14:50, sala: 27</t>
+  </si>
+  <si>
+    <t>20.05.2026, 4, 10:35-11:20, sala: 17</t>
+  </si>
+  <si>
+    <t>Nowak Damiana</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>p. Nowak, historia za piątek 22.05.2026</t>
   </si>
   <si>
     <t>20.05.2026, 5, 11:25-12:10, sala: 17</t>
@@ -653,7 +671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{89a34cc4-1fb2-4fa0-924e-7163f93c005b}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5bc0308d-ebdd-439f-bb43-562366053fb9}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -674,8 +692,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0adfa307-4275-44af-ae00-344989bf5983}">
-  <dimension ref="A1:G12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{00f602f9-5518-4406-90e8-a5e75998b119}">
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="32.5714285714286" customWidth="1"/>
@@ -878,27 +896,27 @@
         <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
         <v>24</v>
@@ -907,7 +925,7 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
@@ -918,25 +936,25 @@
     </row>
     <row r="11" spans="1:7" ht="15">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15">
@@ -960,6 +978,29 @@
       </c>
       <c r="G12" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
   <si>
-    <t>Okres: 18.05.2026 (pon.) - 24.05.2026 (niedz.)</t>
+    <t>Okres: 25.05.2026 (pon.) - 30.05.2026 (sob.)</t>
   </si>
   <si>
     <t>Przeniesiono z</t>
@@ -47,181 +47,70 @@
     <t>Uwagi</t>
   </si>
   <si>
-    <t>18.05.2026, 8, 14:05-14:50, sala: prF3</t>
-  </si>
-  <si>
-    <t>18.05.2026, 7, 13:15-14:00, sala: prF3</t>
-  </si>
-  <si>
-    <t>Sobczak Anna</t>
+    <t>27.05.2026, 8, 14:05-14:50, sala: 3</t>
+  </si>
+  <si>
+    <t>26.05.2026, 5, 11:25-12:10, sala: 17</t>
+  </si>
+  <si>
+    <t>Biczysko Wojciech</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3FA</t>
-  </si>
-  <si>
-    <t>Techniki fryzjerskie</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>18.05.2026, 1, 08:00-08:45, sala: 18</t>
-  </si>
-  <si>
-    <t>18.05.2026, 10, 15:45-16:30, sala: 40</t>
-  </si>
-  <si>
-    <t>Jarek Zbigniew</t>
-  </si>
-  <si>
-    <t>1TH|JA2</t>
-  </si>
-  <si>
-    <t>Edukacja dla bezpieczeństwa</t>
-  </si>
-  <si>
-    <t>lekcja przeniesiona na lekcję 10, sala 40</t>
-  </si>
-  <si>
-    <t>19.05.2026, 7, 13:15-14:00, sala: 17</t>
-  </si>
-  <si>
-    <t>19.05.2026, 2, 08:50-09:35, sala: 17</t>
-  </si>
-  <si>
-    <t>Fiodorów Małgorzata</t>
-  </si>
-  <si>
-    <t>1TFB|JA1</t>
+    <t>3TFB</t>
+  </si>
+  <si>
+    <t>Fizyka</t>
+  </si>
+  <si>
+    <t>p. Biczysko, fizyka za środę. Przeniesiona na wtorek, lekcja 5, sala 17</t>
+  </si>
+  <si>
+    <t>26.05.2026, 6, 12:25-13:10, sala: 17</t>
+  </si>
+  <si>
+    <t>27.05.2026, 1, 08:00-08:45, sala: 3</t>
+  </si>
+  <si>
+    <t>Filusz Marzena</t>
+  </si>
+  <si>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - matematyka w działalności gospodarczej</t>
+  </si>
+  <si>
+    <t>RKZ przeniesione na środę 27.05.2026 lekcja 1</t>
+  </si>
+  <si>
+    <t>25.05.2026, 2, 08:50-09:35, sala: 44</t>
+  </si>
+  <si>
+    <t>27.05.2026, 2, 08:50-09:35, sala: 44</t>
+  </si>
+  <si>
+    <t>Misiąg Anna</t>
+  </si>
+  <si>
+    <t>2TFA</t>
   </si>
   <si>
     <t>Język niemiecki</t>
   </si>
   <si>
-    <t>lekcja przeniesiona na lekcję 2, sala 17</t>
-  </si>
-  <si>
-    <t>19.05.2026, 2, 08:50-09:35, sala: sg6</t>
-  </si>
-  <si>
-    <t>19.05.2026, 5, 11:25-12:10, sala: sg6</t>
-  </si>
-  <si>
-    <t>Pietrycha Małgorzata</t>
-  </si>
-  <si>
-    <t>2FB|DZ</t>
-  </si>
-  <si>
-    <t>Wychowanie fizyczne</t>
-  </si>
-  <si>
-    <t>20.05.2026, 2, 08:50-09:35, sala: 17</t>
-  </si>
-  <si>
-    <t>4TH</t>
-  </si>
-  <si>
-    <t>20.05.2026, 1, 08:00-08:45, sala: 22</t>
-  </si>
-  <si>
-    <t>20.05.2026, 2, 08:50-09:35, sala: 22</t>
-  </si>
-  <si>
-    <t>Ulanowska Magdalena</t>
-  </si>
-  <si>
-    <t>2TH</t>
-  </si>
-  <si>
-    <t>Język polski</t>
-  </si>
-  <si>
-    <t>20.05.2026, 3, 09:40-10:25, sala: 40</t>
-  </si>
-  <si>
-    <t>20.05.2026, 3, 09:40-10:25, sala: bib</t>
-  </si>
-  <si>
-    <t>Socha Dariusz</t>
-  </si>
-  <si>
-    <t>Zajęcia biblioteczne</t>
-  </si>
-  <si>
-    <t>zaplanowano zastępstwo z nauczycielem Nowak Damiana [DW]</t>
-  </si>
-  <si>
-    <t>22.05.2026, 8, 14:05-14:50, sala: 27</t>
-  </si>
-  <si>
-    <t>20.05.2026, 4, 10:35-11:20, sala: 17</t>
-  </si>
-  <si>
-    <t>Nowak Damiana</t>
-  </si>
-  <si>
-    <t>2CA</t>
-  </si>
-  <si>
-    <t>Historia</t>
-  </si>
-  <si>
-    <t>p. Nowak, historia za piątek 22.05.2026</t>
-  </si>
-  <si>
-    <t>20.05.2026, 5, 11:25-12:10, sala: 17</t>
-  </si>
-  <si>
-    <t>20.05.2026, 5, 11:25-12:10, sala: 34</t>
-  </si>
-  <si>
-    <t>20.05.2026, 6, 12:25-13:10, sala: 17</t>
-  </si>
-  <si>
-    <t>20.05.2026, 6, 12:25-13:10, sala: 34</t>
-  </si>
-  <si>
-    <t>3TFA|JA1</t>
-  </si>
-  <si>
-    <t>18.05.2026, 3, 09:40-10:25, sala: 5</t>
-  </si>
-  <si>
-    <t>20.05.2026, 6, 12:25-13:10, sala: 3</t>
-  </si>
-  <si>
-    <t>Krzemińska Beata</t>
-  </si>
-  <si>
-    <t>3TFB</t>
-  </si>
-  <si>
-    <t>Projektowanie fryzur</t>
-  </si>
-  <si>
-    <t>lekcja przeniesiona na środę, 20 maja, lekcja 6, sala 3</t>
-  </si>
-  <si>
-    <t>22.05.2026, 10, 15:45-16:30, sala: 19</t>
-  </si>
-  <si>
-    <t>22.05.2026, 5, 11:25-12:10, sala: 17</t>
-  </si>
-  <si>
-    <t>Biczysko Wojciech</t>
-  </si>
-  <si>
-    <t>1TH</t>
-  </si>
-  <si>
-    <t>Fizyka</t>
-  </si>
-  <si>
-    <t>p. Biczysko, za lekcję 10, sala 17</t>
+    <t>przeniesienie na środę, 27.05.2026 2 lekcja, sala 44</t>
+  </si>
+  <si>
+    <t>27.05.2026, 6, 12:25-13:10, sala: 3</t>
+  </si>
+  <si>
+    <t>Matematyka</t>
+  </si>
+  <si>
+    <t>matematyka przeniesiona na środę 27.05.2026, lekcja 6, sala 3</t>
   </si>
 </sst>
 </file>
@@ -671,7 +560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5bc0308d-ebdd-439f-bb43-562366053fb9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a985d6d5-181c-49d1-8f84-4a6bffa0816e}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -692,16 +581,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{00f602f9-5518-4406-90e8-a5e75998b119}">
-  <dimension ref="A1:G13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{aba1f910-acba-4f0c-887b-ccb76f104983}">
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="32.5714285714286" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="1" max="2" width="30.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="26.7142857142857" customWidth="1"/>
-    <col min="7" max="7" width="56.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="68.4285714285714" customWidth="1"/>
+    <col min="7" max="7" width="60.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
@@ -798,209 +687,25 @@
     </row>
     <row r="5" spans="1:7" ht="15">
       <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
         <v>28</v>
       </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15">
-      <c r="A8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15">
-      <c r="A9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15">
-      <c r="A10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15">
-      <c r="A11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
   <si>
-    <t>Okres: 25.05.2026 (pon.) - 30.05.2026 (sob.)</t>
+    <t>Okres: 25.05.2026 (pon.) - 31.05.2026 (niedz.)</t>
   </si>
   <si>
     <t>Przeniesiono z</t>
@@ -47,6 +47,33 @@
     <t>Uwagi</t>
   </si>
   <si>
+    <t>25.05.2026, 8, 14:05-14:50, sala: 5</t>
+  </si>
+  <si>
+    <t>25.05.2026, 8, 14:05-14:50, sala: 4</t>
+  </si>
+  <si>
+    <t>Danielewski Paweł</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>Techniki fryzjerskie</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>25.05.2026, 9, 14:55-15:40, sala: 5</t>
+  </si>
+  <si>
+    <t>25.05.2026, 9, 14:55-15:40, sala: 4</t>
+  </si>
+  <si>
     <t>27.05.2026, 8, 14:05-14:50, sala: 3</t>
   </si>
   <si>
@@ -56,9 +83,6 @@
     <t>Biczysko Wojciech</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>3TFB</t>
   </si>
   <si>
@@ -75,9 +99,6 @@
   </si>
   <si>
     <t>Filusz Marzena</t>
-  </si>
-  <si>
-    <t>3TFA</t>
   </si>
   <si>
     <t>Rozwój kompetencji zawodowych - matematyka w działalności gospodarczej</t>
@@ -560,7 +581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a985d6d5-181c-49d1-8f84-4a6bffa0816e}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{22f0d1a9-5287-4b4f-a564-5ad495465908}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -581,8 +602,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{aba1f910-acba-4f0c-887b-ccb76f104983}">
-  <dimension ref="A1:G5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c4e85857-ce7b-42a9-85d8-03f6a3d400bf}">
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7142857142857" customWidth="1"/>
@@ -647,53 +668,53 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
@@ -702,10 +723,56 @@
         <v>13</v>
       </c>
       <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15">
+      <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="G5" t="s">
+      <c r="B6" t="s">
         <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="59">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -74,6 +74,39 @@
     <t>25.05.2026, 9, 14:55-15:40, sala: 4</t>
   </si>
   <si>
+    <t>25.05.2026, 8, 14:05-14:50, sala: 43</t>
+  </si>
+  <si>
+    <t>26.05.2026, 2, 08:50-09:35, sala: 43</t>
+  </si>
+  <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>2TH</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>p. Granatowska, j. angielski z poniedziałku 25 maja</t>
+  </si>
+  <si>
+    <t>26.05.2026, 1, 08:00-08:45, sala: 2</t>
+  </si>
+  <si>
+    <t>26.05.2026, 3, 09:40-10:25, sala: 2</t>
+  </si>
+  <si>
+    <t>Marzec Renata</t>
+  </si>
+  <si>
+    <t>1CA</t>
+  </si>
+  <si>
+    <t>Technika w produkcji cukierniczej</t>
+  </si>
+  <si>
     <t>27.05.2026, 8, 14:05-14:50, sala: 3</t>
   </si>
   <si>
@@ -90,6 +123,36 @@
   </si>
   <si>
     <t>p. Biczysko, fizyka za środę. Przeniesiona na wtorek, lekcja 5, sala 17</t>
+  </si>
+  <si>
+    <t>26.05.2026, 7, 13:15-14:00, sala: 2</t>
+  </si>
+  <si>
+    <t>26.05.2026, 6, 12:25-13:10, sala: 2</t>
+  </si>
+  <si>
+    <t>Mikołajczak Sylwia</t>
+  </si>
+  <si>
+    <t>1TFA</t>
+  </si>
+  <si>
+    <t>Podstawy fryzjerstwa</t>
+  </si>
+  <si>
+    <t>26.05.2026, 10, 15:45-16:30, sala: 4</t>
+  </si>
+  <si>
+    <t>26.05.2026, 9, 14:55-15:40, sala: 4</t>
+  </si>
+  <si>
+    <t>Kopij Marcin</t>
+  </si>
+  <si>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>Edukacja obywatelska</t>
   </si>
   <si>
     <t>26.05.2026, 6, 12:25-13:10, sala: 17</t>
@@ -581,7 +644,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{22f0d1a9-5287-4b4f-a564-5ad495465908}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{09c11060-279a-4a6b-8776-e3f69f2c6914}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -602,12 +665,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c4e85857-ce7b-42a9-85d8-03f6a3d400bf}">
-  <dimension ref="A1:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ca9dba25-6ba9-4778-add1-4aa2bb722f00}">
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="19.8571428571429" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="68.4285714285714" customWidth="1"/>
@@ -720,13 +783,13 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15">
@@ -754,25 +817,117 @@
     </row>
     <row r="7" spans="1:7" ht="15">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -170,6 +170,18 @@
     <t>RKZ przeniesione na środę 27.05.2026 lekcja 1</t>
   </si>
   <si>
+    <t>28.05.2026, 1, 08:00-08:45, sala: 4</t>
+  </si>
+  <si>
+    <t>27.05.2026, 2, 08:50-09:35, sala: 4</t>
+  </si>
+  <si>
+    <t>2S</t>
+  </si>
+  <si>
+    <t>p. Kopij, edukacja obywatelska za czwartek 28 maja 2026</t>
+  </si>
+  <si>
     <t>25.05.2026, 2, 08:50-09:35, sala: 44</t>
   </si>
   <si>
@@ -188,6 +200,21 @@
     <t>przeniesienie na środę, 27.05.2026 2 lekcja, sala 44</t>
   </si>
   <si>
+    <t>27.05.2026, 1, 08:00-08:45, sala: 18</t>
+  </si>
+  <si>
+    <t>27.05.2026, 3, 09:40-10:25, sala: 18</t>
+  </si>
+  <si>
+    <t>Piątek-Pawłowska Bożena</t>
+  </si>
+  <si>
+    <t>1FA</t>
+  </si>
+  <si>
+    <t>Język polski</t>
+  </si>
+  <si>
     <t>27.05.2026, 6, 12:25-13:10, sala: 3</t>
   </si>
   <si>
@@ -195,6 +222,30 @@
   </si>
   <si>
     <t>matematyka przeniesiona na środę 27.05.2026, lekcja 6, sala 3</t>
+  </si>
+  <si>
+    <t>27.05.2026, 1, 08:00-08:45, sala: 5</t>
+  </si>
+  <si>
+    <t>27.05.2026, 6, 12:25-13:10, sala: 5</t>
+  </si>
+  <si>
+    <t>Krzemińska Beata</t>
+  </si>
+  <si>
+    <t>p. Krzemińska, techniki za lekcję 1</t>
+  </si>
+  <si>
+    <t>28.05.2026, 7, 13:15-14:00, sala: 26</t>
+  </si>
+  <si>
+    <t>28.05.2026, 5, 11:25-12:10, sala: 26</t>
+  </si>
+  <si>
+    <t>Hudziec Agnieszka</t>
+  </si>
+  <si>
+    <t>Chemia</t>
   </si>
 </sst>
 </file>
@@ -644,7 +695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{09c11060-279a-4a6b-8776-e3f69f2c6914}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{74699cb4-3ad5-4e99-82b6-7fc130b143d2}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -665,12 +716,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ca9dba25-6ba9-4778-add1-4aa2bb722f00}">
-  <dimension ref="A1:G11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{7a442445-ac78-42f7-bd3f-30e31b0defef}">
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="19.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="24.2857142857143" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="68.4285714285714" customWidth="1"/>
@@ -892,42 +943,134 @@
         <v>51</v>
       </c>
       <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
         <v>52</v>
       </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" t="s">
         <v>53</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15">
       <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15">
+      <c r="A13" t="s">
         <v>30</v>
       </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" t="s">
         <v>47</v>
       </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
         <v>32</v>
       </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" t="s">
-        <v>58</v>
+      <c r="F13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15">
+      <c r="A14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15">
+      <c r="A15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -155,21 +155,6 @@
     <t>Edukacja obywatelska</t>
   </si>
   <si>
-    <t>26.05.2026, 6, 12:25-13:10, sala: 17</t>
-  </si>
-  <si>
-    <t>27.05.2026, 1, 08:00-08:45, sala: 3</t>
-  </si>
-  <si>
-    <t>Filusz Marzena</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - matematyka w działalności gospodarczej</t>
-  </si>
-  <si>
-    <t>RKZ przeniesione na środę 27.05.2026 lekcja 1</t>
-  </si>
-  <si>
     <t>28.05.2026, 1, 08:00-08:45, sala: 4</t>
   </si>
   <si>
@@ -215,15 +200,6 @@
     <t>Język polski</t>
   </si>
   <si>
-    <t>27.05.2026, 6, 12:25-13:10, sala: 3</t>
-  </si>
-  <si>
-    <t>Matematyka</t>
-  </si>
-  <si>
-    <t>matematyka przeniesiona na środę 27.05.2026, lekcja 6, sala 3</t>
-  </si>
-  <si>
     <t>27.05.2026, 1, 08:00-08:45, sala: 5</t>
   </si>
   <si>
@@ -236,6 +212,18 @@
     <t>p. Krzemińska, techniki za lekcję 1</t>
   </si>
   <si>
+    <t>27.05.2026, 8, 14:05-14:50, sala: 32</t>
+  </si>
+  <si>
+    <t>27.05.2026, 7, 13:15-14:00, sala: 32</t>
+  </si>
+  <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
+    <t>3TFA|JA1</t>
+  </si>
+  <si>
     <t>28.05.2026, 7, 13:15-14:00, sala: 26</t>
   </si>
   <si>
@@ -246,6 +234,18 @@
   </si>
   <si>
     <t>Chemia</t>
+  </si>
+  <si>
+    <t>29.05.2026, 3, 09:40-10:25, sala: 30</t>
+  </si>
+  <si>
+    <t>29.05.2026, 7, 13:15-14:00, sala: 30</t>
+  </si>
+  <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
+    <t>2FC</t>
   </si>
 </sst>
 </file>
@@ -695,7 +695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{74699cb4-3ad5-4e99-82b6-7fc130b143d2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{699ebda1-6bbd-4126-8a0f-f00aa042c1d0}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -716,7 +716,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{7a442445-ac78-42f7-bd3f-30e31b0defef}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5d26b8e7-67ac-44d0-89a1-9d225b439a66}">
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -724,7 +724,7 @@
     <col min="3" max="3" width="24.2857142857143" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="68.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="30.8571428571429" customWidth="1"/>
     <col min="7" max="7" width="60.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
@@ -920,30 +920,30 @@
         <v>46</v>
       </c>
       <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
         <v>47</v>
       </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
       <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" t="s">
         <v>48</v>
-      </c>
-      <c r="G9" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15">
       <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
         <v>50</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>51</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -952,33 +952,33 @@
         <v>52</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15">
@@ -995,36 +995,36 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
         <v>63</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
         <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="G13" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15">
@@ -1041,13 +1041,13 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15">
@@ -1064,10 +1064,10 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="86">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -200,6 +200,24 @@
     <t>Język polski</t>
   </si>
   <si>
+    <t>29.05.2026, 8, 14:05-14:50, sala: 27</t>
+  </si>
+  <si>
+    <t>27.05.2026, 4, 10:35-11:20, sala: 19</t>
+  </si>
+  <si>
+    <t>Nowak Damiana</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>p. Nowak Damiana, historia za piątek 29 maja</t>
+  </si>
+  <si>
     <t>27.05.2026, 1, 08:00-08:45, sala: 5</t>
   </si>
   <si>
@@ -234,6 +252,18 @@
   </si>
   <si>
     <t>Chemia</t>
+  </si>
+  <si>
+    <t>28.05.2026, 10, 15:45-16:30, sala: 09</t>
+  </si>
+  <si>
+    <t>28.05.2026, 9, 14:55-15:40, sala: 09</t>
+  </si>
+  <si>
+    <t>Leńczowska Iwona</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - Fryzjerstwo naturalne</t>
   </si>
   <si>
     <t>29.05.2026, 3, 09:40-10:25, sala: 30</t>
@@ -695,7 +725,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{699ebda1-6bbd-4126-8a0f-f00aa042c1d0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{53de23c9-b3f4-4151-8f54-cc965a87e0a9}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -716,15 +746,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5d26b8e7-67ac-44d0-89a1-9d225b439a66}">
-  <dimension ref="A1:G15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{3d3a3341-3e91-4bff-84a7-f83f836e66f6}">
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="30.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="31.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="30.7142857142857" customWidth="1"/>
     <col min="3" max="3" width="24.2857142857143" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="30.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="52" customWidth="1"/>
     <col min="7" max="7" width="60.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
@@ -995,56 +1026,56 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="G12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="F14" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
@@ -1052,24 +1083,70 @@
     </row>
     <row r="15" spans="1:7" ht="15">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15">
+      <c r="A17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" t="s">
         <v>59</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G17" t="s">
         <v>15</v>
       </c>
     </row>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="82">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -252,18 +252,6 @@
   </si>
   <si>
     <t>Chemia</t>
-  </si>
-  <si>
-    <t>28.05.2026, 10, 15:45-16:30, sala: 09</t>
-  </si>
-  <si>
-    <t>28.05.2026, 9, 14:55-15:40, sala: 09</t>
-  </si>
-  <si>
-    <t>Leńczowska Iwona</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - Fryzjerstwo naturalne</t>
   </si>
   <si>
     <t>29.05.2026, 3, 09:40-10:25, sala: 30</t>
@@ -725,7 +713,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{53de23c9-b3f4-4151-8f54-cc965a87e0a9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{7e09aef4-deb0-43d4-a4f8-bcbe39059155}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -746,16 +734,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{3d3a3341-3e91-4bff-84a7-f83f836e66f6}">
-  <dimension ref="A1:G17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4f80306d-3700-471d-a8f9-25c8f1e8030f}">
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="30.7142857142857" customWidth="1"/>
+    <col min="1" max="2" width="30.7142857142857" customWidth="1"/>
     <col min="3" max="3" width="24.2857142857143" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="52" customWidth="1"/>
+    <col min="6" max="6" width="30.8571428571429" customWidth="1"/>
     <col min="7" max="7" width="60.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1118,35 +1105,12 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="F16" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15">
-      <c r="A17" t="s">
-        <v>82</v>
-      </c>
-      <c r="B17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" t="s">
-        <v>85</v>
-      </c>
-      <c r="F17" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17" t="s">
         <v>15</v>
       </c>
     </row>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
   <si>
-    <t>Okres: 25.05.2026 (pon.) - 31.05.2026 (niedz.)</t>
+    <t>Okres: 08.06.2026 (pon.) - 14.06.2026 (niedz.)</t>
   </si>
   <si>
     <t>Przeniesiono z</t>
@@ -47,223 +47,43 @@
     <t>Uwagi</t>
   </si>
   <si>
-    <t>25.05.2026, 8, 14:05-14:50, sala: 5</t>
-  </si>
-  <si>
-    <t>25.05.2026, 8, 14:05-14:50, sala: 4</t>
-  </si>
-  <si>
-    <t>Danielewski Paweł</t>
+    <t>08.06.2026, 7, 13:15-14:00, sala: 18</t>
+  </si>
+  <si>
+    <t>08.06.2026, 6, 12:25-13:10, sala: 18</t>
+  </si>
+  <si>
+    <t>Nowak Damiana</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3TFA</t>
-  </si>
-  <si>
-    <t>Techniki fryzjerskie</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>25.05.2026, 9, 14:55-15:40, sala: 5</t>
-  </si>
-  <si>
-    <t>25.05.2026, 9, 14:55-15:40, sala: 4</t>
-  </si>
-  <si>
-    <t>25.05.2026, 8, 14:05-14:50, sala: 43</t>
-  </si>
-  <si>
-    <t>26.05.2026, 2, 08:50-09:35, sala: 43</t>
-  </si>
-  <si>
-    <t>Granatowska Mariola</t>
-  </si>
-  <si>
-    <t>2TH</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>p. Granatowska, j. angielski z poniedziałku 25 maja</t>
-  </si>
-  <si>
-    <t>26.05.2026, 1, 08:00-08:45, sala: 2</t>
-  </si>
-  <si>
-    <t>26.05.2026, 3, 09:40-10:25, sala: 2</t>
-  </si>
-  <si>
-    <t>Marzec Renata</t>
-  </si>
-  <si>
-    <t>1CA</t>
-  </si>
-  <si>
-    <t>Technika w produkcji cukierniczej</t>
-  </si>
-  <si>
-    <t>27.05.2026, 8, 14:05-14:50, sala: 3</t>
-  </si>
-  <si>
-    <t>26.05.2026, 5, 11:25-12:10, sala: 17</t>
-  </si>
-  <si>
-    <t>Biczysko Wojciech</t>
-  </si>
-  <si>
-    <t>3TFB</t>
-  </si>
-  <si>
-    <t>Fizyka</t>
-  </si>
-  <si>
-    <t>p. Biczysko, fizyka za środę. Przeniesiona na wtorek, lekcja 5, sala 17</t>
-  </si>
-  <si>
-    <t>26.05.2026, 7, 13:15-14:00, sala: 2</t>
-  </si>
-  <si>
-    <t>26.05.2026, 6, 12:25-13:10, sala: 2</t>
-  </si>
-  <si>
-    <t>Mikołajczak Sylwia</t>
-  </si>
-  <si>
-    <t>1TFA</t>
-  </si>
-  <si>
-    <t>Podstawy fryzjerstwa</t>
-  </si>
-  <si>
-    <t>26.05.2026, 10, 15:45-16:30, sala: 4</t>
-  </si>
-  <si>
-    <t>26.05.2026, 9, 14:55-15:40, sala: 4</t>
-  </si>
-  <si>
-    <t>Kopij Marcin</t>
-  </si>
-  <si>
-    <t>2FB</t>
-  </si>
-  <si>
-    <t>Edukacja obywatelska</t>
-  </si>
-  <si>
-    <t>28.05.2026, 1, 08:00-08:45, sala: 4</t>
-  </si>
-  <si>
-    <t>27.05.2026, 2, 08:50-09:35, sala: 4</t>
-  </si>
-  <si>
-    <t>2S</t>
-  </si>
-  <si>
-    <t>p. Kopij, edukacja obywatelska za czwartek 28 maja 2026</t>
-  </si>
-  <si>
-    <t>25.05.2026, 2, 08:50-09:35, sala: 44</t>
-  </si>
-  <si>
-    <t>27.05.2026, 2, 08:50-09:35, sala: 44</t>
-  </si>
-  <si>
-    <t>Misiąg Anna</t>
-  </si>
-  <si>
-    <t>2TFA</t>
-  </si>
-  <si>
-    <t>Język niemiecki</t>
-  </si>
-  <si>
-    <t>przeniesienie na środę, 27.05.2026 2 lekcja, sala 44</t>
-  </si>
-  <si>
-    <t>27.05.2026, 1, 08:00-08:45, sala: 18</t>
-  </si>
-  <si>
-    <t>27.05.2026, 3, 09:40-10:25, sala: 18</t>
-  </si>
-  <si>
-    <t>Piątek-Pawłowska Bożena</t>
-  </si>
-  <si>
-    <t>1FA</t>
-  </si>
-  <si>
-    <t>Język polski</t>
-  </si>
-  <si>
-    <t>29.05.2026, 8, 14:05-14:50, sala: 27</t>
-  </si>
-  <si>
-    <t>27.05.2026, 4, 10:35-11:20, sala: 19</t>
-  </si>
-  <si>
-    <t>Nowak Damiana</t>
-  </si>
-  <si>
-    <t>2CA</t>
+    <t>2TFB</t>
   </si>
   <si>
     <t>Historia</t>
   </si>
   <si>
-    <t>p. Nowak Damiana, historia za piątek 29 maja</t>
-  </si>
-  <si>
-    <t>27.05.2026, 1, 08:00-08:45, sala: 5</t>
-  </si>
-  <si>
-    <t>27.05.2026, 6, 12:25-13:10, sala: 5</t>
-  </si>
-  <si>
-    <t>Krzemińska Beata</t>
-  </si>
-  <si>
-    <t>p. Krzemińska, techniki za lekcję 1</t>
-  </si>
-  <si>
-    <t>27.05.2026, 8, 14:05-14:50, sala: 32</t>
-  </si>
-  <si>
-    <t>27.05.2026, 7, 13:15-14:00, sala: 32</t>
-  </si>
-  <si>
-    <t>Wojciechowski Łukasz</t>
-  </si>
-  <si>
-    <t>3TFA|JA1</t>
-  </si>
-  <si>
-    <t>28.05.2026, 7, 13:15-14:00, sala: 26</t>
-  </si>
-  <si>
-    <t>28.05.2026, 5, 11:25-12:10, sala: 26</t>
-  </si>
-  <si>
-    <t>Hudziec Agnieszka</t>
-  </si>
-  <si>
-    <t>Chemia</t>
-  </si>
-  <si>
-    <t>29.05.2026, 3, 09:40-10:25, sala: 30</t>
-  </si>
-  <si>
-    <t>29.05.2026, 7, 13:15-14:00, sala: 30</t>
-  </si>
-  <si>
-    <t>Filipek Anna</t>
-  </si>
-  <si>
-    <t>2FC</t>
+    <t>p. Nowak, historia za lekcję 7</t>
+  </si>
+  <si>
+    <t>08.06.2026, 3, 09:40-10:25, sala: 28</t>
+  </si>
+  <si>
+    <t>08.06.2026, 7, 13:15-14:00, sala: 5</t>
+  </si>
+  <si>
+    <t>Sałdyka Karolina</t>
+  </si>
+  <si>
+    <t>4TFB</t>
+  </si>
+  <si>
+    <t>Biologia</t>
+  </si>
+  <si>
+    <t>p. Sałdyka, biologia przeniesiona na lekcję 7, sala nr 5</t>
   </si>
 </sst>
 </file>
@@ -713,7 +533,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{7e09aef4-deb0-43d4-a4f8-bcbe39059155}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{25e27d1d-c186-4a28-8be3-53617171b9ac}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -734,16 +554,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4f80306d-3700-471d-a8f9-25c8f1e8030f}">
-  <dimension ref="A1:G16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0e84e2fb-fd24-442a-8f8c-ef91fedc492f}">
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="24.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="30.8571428571429" customWidth="1"/>
-    <col min="7" max="7" width="60.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="47.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
@@ -800,318 +620,19 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
         <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15">
-      <c r="A8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15">
-      <c r="A9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15">
-      <c r="A10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15">
-      <c r="A11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15">
-      <c r="A12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15">
-      <c r="A13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15">
-      <c r="A14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" t="s">
-        <v>73</v>
-      </c>
-      <c r="F14" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15">
-      <c r="A15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15">
-      <c r="A16" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" t="s">
-        <v>81</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -533,7 +533,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{25e27d1d-c186-4a28-8be3-53617171b9ac}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d65196f8-8a1a-4229-801b-dd6c3bcf6c21}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -554,7 +554,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0e84e2fb-fd24-442a-8f8c-ef91fedc492f}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{53e51272-d463-4d53-9d16-72366bc47cad}">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -84,6 +84,75 @@
   </si>
   <si>
     <t>p. Sałdyka, biologia przeniesiona na lekcję 7, sala nr 5</t>
+  </si>
+  <si>
+    <t>09.06.2026, 7, 13:15-14:00, sala: 27</t>
+  </si>
+  <si>
+    <t>09.06.2026, 5, 11:25-12:10, sala: 27</t>
+  </si>
+  <si>
+    <t>Karczmarz Aleksandra</t>
+  </si>
+  <si>
+    <t>1TFB|JA2</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>p. Karczmarz, j. angielski przeniesiony na lekcję 5, sala 27</t>
+  </si>
+  <si>
+    <t>09.06.2026, 2, 08:50-09:35, sala: 34</t>
+  </si>
+  <si>
+    <t>09.06.2026, 5, 11:25-12:10, sala: 34</t>
+  </si>
+  <si>
+    <t>Mucha Anna</t>
+  </si>
+  <si>
+    <t>3FB</t>
+  </si>
+  <si>
+    <t>p. Mucha, biologia za lekcję 2, sala 34 lekcja 5</t>
+  </si>
+  <si>
+    <t>09.06.2026, 9, 14:55-15:40, sala: 23</t>
+  </si>
+  <si>
+    <t>09.06.2026, 8, 14:05-14:50, sala: 23</t>
+  </si>
+  <si>
+    <t>Nowaczyk Agnieszka</t>
+  </si>
+  <si>
+    <t>3K</t>
+  </si>
+  <si>
+    <t>Język angielski zawodowy</t>
+  </si>
+  <si>
+    <t>p. Nowaczyk, j. angielski przeniesiony na lekcję 8</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>p. Nowaczyk, j. angielski przeniesiony na lekcję 9</t>
+  </si>
+  <si>
+    <t>09.06.2026, 1, 08:00-08:45, sala: 28</t>
+  </si>
+  <si>
+    <t>10.06.2026, 1, 08:00-08:45, sala: 3</t>
+  </si>
+  <si>
+    <t>3TFB</t>
+  </si>
+  <si>
+    <t>biologia przeniesiona na środę, 10.06.2026 1 lekcja, sala 3</t>
   </si>
 </sst>
 </file>
@@ -533,7 +602,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d65196f8-8a1a-4229-801b-dd6c3bcf6c21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8c369f6b-2e3d-4e8a-a1e0-7a33f2978a4e}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -554,16 +623,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{53e51272-d463-4d53-9d16-72366bc47cad}">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c8060177-9ba1-4bc2-855c-b548887a2afb}">
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="20.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="47.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="51.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
@@ -633,6 +702,121 @@
       </c>
       <c r="G3" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -119,30 +119,6 @@
     <t>p. Mucha, biologia za lekcję 2, sala 34 lekcja 5</t>
   </si>
   <si>
-    <t>09.06.2026, 9, 14:55-15:40, sala: 23</t>
-  </si>
-  <si>
-    <t>09.06.2026, 8, 14:05-14:50, sala: 23</t>
-  </si>
-  <si>
-    <t>Nowaczyk Agnieszka</t>
-  </si>
-  <si>
-    <t>3K</t>
-  </si>
-  <si>
-    <t>Język angielski zawodowy</t>
-  </si>
-  <si>
-    <t>p. Nowaczyk, j. angielski przeniesiony na lekcję 8</t>
-  </si>
-  <si>
-    <t>2B</t>
-  </si>
-  <si>
-    <t>p. Nowaczyk, j. angielski przeniesiony na lekcję 9</t>
-  </si>
-  <si>
     <t>09.06.2026, 1, 08:00-08:45, sala: 28</t>
   </si>
   <si>
@@ -153,6 +129,63 @@
   </si>
   <si>
     <t>biologia przeniesiona na środę, 10.06.2026 1 lekcja, sala 3</t>
+  </si>
+  <si>
+    <t>10.06.2026, 9, 14:55-15:40, sala: 29</t>
+  </si>
+  <si>
+    <t>10.06.2026, 6, 12:25-13:10, sala: 29</t>
+  </si>
+  <si>
+    <t>Bujanowska Iwona</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>Matematyka</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>10.06.2026, 7, 13:15-14:00, sala: 30</t>
+  </si>
+  <si>
+    <t>10.06.2026, 6, 12:25-13:10, sala: 30</t>
+  </si>
+  <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
+    <t>2FA</t>
+  </si>
+  <si>
+    <t>Język polski</t>
+  </si>
+  <si>
+    <t>10.06.2026, 9, 14:55-15:40, sala: 18</t>
+  </si>
+  <si>
+    <t>10.06.2026, 8, 14:05-14:50, sala: 18</t>
+  </si>
+  <si>
+    <t>2CB</t>
+  </si>
+  <si>
+    <t>12.06.2026, 8, 14:05-14:50, sala: 19</t>
+  </si>
+  <si>
+    <t>12.06.2026, 5, 11:25-12:10, sala: 19</t>
+  </si>
+  <si>
+    <t>Biczysko Wojciech</t>
+  </si>
+  <si>
+    <t>1TFA</t>
+  </si>
+  <si>
+    <t>Fizyka</t>
   </si>
 </sst>
 </file>
@@ -602,7 +635,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8c369f6b-2e3d-4e8a-a1e0-7a33f2978a4e}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{97f6739a-2916-43f8-bb28-b524e4048c1e}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -623,15 +656,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c8060177-9ba1-4bc2-855c-b548887a2afb}">
-  <dimension ref="A1:G8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4474526f-cc1a-4f0f-9972-b920eda60ca4}">
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7142857142857" customWidth="1"/>
     <col min="3" max="3" width="20.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="6" max="6" width="14.1428571428571" customWidth="1"/>
     <col min="7" max="7" width="51.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
@@ -758,65 +791,111 @@
         <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" t="s">
         <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="G8" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -635,7 +635,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{97f6739a-2916-43f8-bb28-b524e4048c1e}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{580aea4e-3921-4eb6-952e-ec87358f8bbf}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -656,7 +656,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4474526f-cc1a-4f0f-9972-b920eda60ca4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d5764043-35fb-42ed-a81d-eef3c759363f}">
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -635,7 +635,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{580aea4e-3921-4eb6-952e-ec87358f8bbf}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2eda9955-ae77-441c-9a73-6af0b8e35dd2}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -656,7 +656,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d5764043-35fb-42ed-a81d-eef3c759363f}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{21e7b59f-f001-4df5-80d7-986311edccde}">
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>

--- a/InformacjeOPrzeniesieniach (1).xlsx
+++ b/InformacjeOPrzeniesieniach (1).xlsx
@@ -635,7 +635,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2eda9955-ae77-441c-9a73-6af0b8e35dd2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{10e9c005-a2e4-4e6e-9c3d-c24ebf3bdd59}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -656,7 +656,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{21e7b59f-f001-4df5-80d7-986311edccde}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{19c737c7-8e23-4553-bdc9-a951fb5adb35}">
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
